--- a/group_visit_counts.xlsx
+++ b/group_visit_counts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aeg00011/Desktop/AD-Research/AD-Early-Prediction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D830531-5600-6C4D-A737-8B6B75B1BE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F246C3-A5AE-394C-B199-31DB448653D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35220" yWindow="940" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
         <v>353</v>
       </c>
       <c r="E3" s="1">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -479,7 +479,7 @@
         <v>174</v>
       </c>
       <c r="E4" s="1">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -496,7 +496,7 @@
         <v>81</v>
       </c>
       <c r="E5" s="1">
-        <v>185</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -513,7 +513,7 @@
         <v>59</v>
       </c>
       <c r="E6" s="1">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -530,7 +530,7 @@
         <v>41</v>
       </c>
       <c r="E7" s="1">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -547,7 +547,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -564,7 +564,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="1">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -581,7 +581,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="1">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/group_visit_counts.xlsx
+++ b/group_visit_counts.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aeg00011/Desktop/AD-Research/AD-Early-Prediction/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F246C3-A5AE-394C-B199-31DB448653D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FADD9F3-E083-594D-8926-E5DCAE0B2BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-2200" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Lit Review Table" sheetId="2" r:id="rId1"/>
+    <sheet name="Group Visits" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
   <si>
     <t>Number of Visits</t>
   </si>
@@ -62,13 +63,220 @@
   </si>
   <si>
     <t>10 Visits</t>
+  </si>
+  <si>
+    <t>Study</t>
+  </si>
+  <si>
+    <t>Dataset(s)</t>
+  </si>
+  <si>
+    <t>Task(s)</t>
+  </si>
+  <si>
+    <t>ML model(s)</t>
+  </si>
+  <si>
+    <t>AUC ROC</t>
+  </si>
+  <si>
+    <t>F1 score</t>
+  </si>
+  <si>
+    <t>Adelson et al. (2023)</t>
+  </si>
+  <si>
+    <t>ADNI [N=493]</t>
+  </si>
+  <si>
+    <t>Binary prediction of MCI‑to‑AD conversion at 12, 24, and 48 months after baseline</t>
+  </si>
+  <si>
+    <t>Cross-sectional</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Alatrany et al. (2024)</t>
+  </si>
+  <si>
+    <t>NACC [N not reported]</t>
+  </si>
+  <si>
+    <t>Binary and multi‑class classification among CN, MCI, and AD at visit time and four‑year follow‑up</t>
+  </si>
+  <si>
+    <t>RF, KNN, NB, SVM</t>
+  </si>
+  <si>
+    <t>Bogdanovic el al. (2022)</t>
+  </si>
+  <si>
+    <t>TADPOLE (from ADNI) [N=9,592]</t>
+  </si>
+  <si>
+    <t>Multi‑class classification among CN, EMCI, LMCI, SMCI, and AD</t>
+  </si>
+  <si>
+    <t>XGBoost, RF</t>
+  </si>
+  <si>
+    <t>0.84 (XGBoost)</t>
+  </si>
+  <si>
+    <t>Ding et al. (2023)</t>
+  </si>
+  <si>
+    <t>ADNI [N=347]</t>
+  </si>
+  <si>
+    <t>Binary prediction of MCI‑to‑AD conversion within two years</t>
+  </si>
+  <si>
+    <t>LSTM, RF</t>
+  </si>
+  <si>
+    <t>0.93 (LSTM)</t>
+  </si>
+  <si>
+    <t>Fernández-Blázquez el al. (2025)</t>
+  </si>
+  <si>
+    <t>ERAD and MADRID+90 [N=845]</t>
+  </si>
+  <si>
+    <t>Binary prediction of CN‑to‑MCI conversion within three years</t>
+  </si>
+  <si>
+    <t>Kavitha el al. (2022)</t>
+  </si>
+  <si>
+    <t>OASIS [N=150]</t>
+  </si>
+  <si>
+    <t>Binary classification of demented vs. non‑demented</t>
+  </si>
+  <si>
+    <t>Liu el al. (2025)</t>
+  </si>
+  <si>
+    <t>NACC [N=25,179]</t>
+  </si>
+  <si>
+    <t>Multi‑class prediction of CN, aMCI, and AD 3–10 years after the last visit</t>
+  </si>
+  <si>
+    <t>Longitudinal</t>
+  </si>
+  <si>
+    <t>LSTM + linear attn., LSTM + transformer</t>
+  </si>
+  <si>
+    <t>0.8601 (LSTM + linear attn.)</t>
+  </si>
+  <si>
+    <t>Pang et al. (2023)</t>
+  </si>
+  <si>
+    <t>NACC [N&gt;882]</t>
+  </si>
+  <si>
+    <t>SVM, RF, LR</t>
+  </si>
+  <si>
+    <t>Tabarestani et al. (2019)</t>
+  </si>
+  <si>
+    <t>ADNI [N=1458]</t>
+  </si>
+  <si>
+    <t>Multi‑class prediction among CN, MCI, and AD at 12, 24, and 36 months after the first visit</t>
+  </si>
+  <si>
+    <t>LSTM, GRU</t>
+  </si>
+  <si>
+    <t>&gt;=0.86 (LSTM)</t>
+  </si>
+  <si>
+    <t>Uddin et al. (2023)</t>
+  </si>
+  <si>
+    <t>Binary classification of AD vs. non‑AD</t>
+  </si>
+  <si>
+    <t>0.96 (XGBoost)</t>
+  </si>
+  <si>
+    <t>0.97 (XGBoost)</t>
+  </si>
+  <si>
+    <t>Wang et al. (2025)</t>
+  </si>
+  <si>
+    <t>NACC [N=2,379]</t>
+  </si>
+  <si>
+    <t>RF, XGBoost, LR</t>
+  </si>
+  <si>
+    <t>0.915 (XGBoost)</t>
+  </si>
+  <si>
+    <t>0.833 (XGBoost)</t>
+  </si>
+  <si>
+    <t>Yi et al. (2023)</t>
+  </si>
+  <si>
+    <t>ADNI [N=547]</t>
+  </si>
+  <si>
+    <t>Multi‑class classification among CN, MCI, and AD</t>
+  </si>
+  <si>
+    <t>XGBoost, RF, Bagging, AdaBoost, NB</t>
+  </si>
+  <si>
+    <t>0.906 (XGBoost)</t>
+  </si>
+  <si>
+    <t>Binary prediction of MCI conversion within 4 years, binary prediction of AD conversion 2-3 years</t>
+  </si>
+  <si>
+    <t>GaussianNB, DT, RF, XGBoost, VC, GB</t>
+  </si>
+  <si>
+    <t>DT, SVM, RF, XGBoost and VC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;= 0.857 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCI  0.714 (LR) , AD &gt;= 0.805 (RF) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification 0.843 (SVM) </t>
+  </si>
+  <si>
+    <t>0.85 (XGBoost + VC)</t>
+  </si>
+  <si>
+    <t>Temporal dimension</t>
+  </si>
+  <si>
+    <t>Longitudinal, Cross-sectional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +285,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -103,9 +318,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,6 +626,332 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8765BF61-9611-1248-85B9-B77241DC803D}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="3" width="79.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.83589999999999998</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.92220000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
